--- a/Modelo_Importacao_Visia.xlsx
+++ b/Modelo_Importacao_Visia.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -462,8 +462,9 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,6 +508,11 @@
           <t>data_fabricacao</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>vira_peca</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -549,6 +555,7 @@
           <t>15/07/2026</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -591,6 +598,7 @@
           <t>16/07/2026</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -610,34 +618,39 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>E-A01-CI01</t>
+          <t>EST-PISO-01</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Painel CAD</t>
+          <t>Estrutura do Piso</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1171166</t>
+          <t>1180001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Célula de Estruturas</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Piso CAD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CI-1-02</t>
+          <t>CI-1-01</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -647,81 +660,130 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Piso CAD</t>
+          <t>EST-TETO-01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Piso CAD 6x3m Padrao</t>
+          <t>Estrutura do Teto</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1161922</t>
+          <t>1180002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Célula de Estruturas</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Teto GRC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>CI-1-01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Monobloco Circulacao</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>E-A01-CI01</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Painel CAD</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1171166</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>CI-1-02</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Monobloco Circulacao</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Teto GRC</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Teto GRC 6x3m Padrao</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1161963</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18/07/2026</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Piso CAD</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Piso CAD 6x3m Padrao</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1161922</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CAD,GRC"</formula1>
+      <formula1>"CAD,GRC,Célula de Estruturas"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -734,10 +796,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,80 +829,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Repita tambem nome_produto e data_programada nas linhas do mesmo produto.</t>
+          <t>3. Cada ocorrencia de peca = 1 unidade fisica.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4. Cada ocorrencia de peca = 1 unidade fisica (peca repetida = mais unidades).</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>COLUNAS:</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>COLUNAS:</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>id_produto - codigo do modulo (ex: CI-1-01) - OBRIGATORIO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>id_produto - codigo do modulo (ex: CI-1-01) - OBRIGATORIO</t>
+          <t>nome_produto - nome do modulo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nome_produto - nome do modulo (ex: Monobloco Circulacao)</t>
+          <t>data_programada - data de entrada na montagem (dd/mm/aaaa)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>data_programada - data de entrada na montagem (dd/mm/aaaa)</t>
+          <t>id_peca - codigo da peca - OBRIGATORIO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>id_peca - codigo da peca (ex: Piso CAD, E-A01-CI01) - OBRIGATORIO</t>
+          <t>nome_peca - descricao da peca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nome_peca - descricao da peca</t>
+          <t>serial - codigo de barras</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>serial - codigo de barras da peca</t>
+          <t>setor_fabrica - CAD, GRC ou Célula de Estruturas</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>setor_fabrica - CAD ou GRC</t>
+          <t>data_fabricacao - data prevista de fabricacao (dd/mm/aaaa)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>data_fabricacao - data prevista de fabricacao (dd/mm/aaaa)</t>
+          <t>vira_peca - SO para estruturas: qual peca CAD/GRC essa estrutura vira</t>
         </is>
       </c>
     </row>
@@ -848,16 +910,37 @@
       <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DICA: pecas com mesmo id_peca e serial sao a mesma peca fisica repetida.</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SOBRE CÉLULA DE ESTRUTURAS:</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cada produto cria suas proprias unidades ao importar.</t>
+          <t>- Use o setor "Célula de Estruturas" para as estruturas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- No campo vira_peca, coloque o id_peca da peca CAD/GRC que ela se tornara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>- Ex: uma estrutura com vira_peca = "Piso CAD" aparece ligada ao Piso CAD no portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>- Para pecas CAD/GRC normais, deixe vira_peca em branco.</t>
         </is>
       </c>
     </row>

--- a/Modelo_Importacao_Visia.xlsx
+++ b/Modelo_Importacao_Visia.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001A2540"/>
         <bgColor rgb="001A2540"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE4FA"/>
+        <bgColor rgb="00EDE4FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,12 +86,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -453,18 +460,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +523,21 @@
           <t>vira_peca</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>vira_nome</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>vira_serial</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>vira_data</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -556,6 +581,9 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -599,6 +627,9 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -641,9 +672,24 @@
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Piso CAD</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Piso CAD 6x3m Padrao</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>1161922</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -688,9 +734,24 @@
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Teto GRC</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Teto GRC 6x3m Padrao</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>1161963</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -736,6 +797,9 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -779,6 +843,9 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -796,14 +863,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="85" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>COMO PREENCHER A IMPORTACAO</t>
         </is>
@@ -837,9 +904,9 @@
       <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>COLUNAS:</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>COLUNAS DA PECA:</t>
         </is>
       </c>
     </row>
@@ -900,47 +967,85 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vira_peca - SO para estruturas: qual peca CAD/GRC essa estrutura vira</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>COLUNAS DA PECA FINAL (so para estruturas / Célula de Estruturas):</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SOBRE CÉLULA DE ESTRUTURAS:</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vira_peca   - ID da peca final que a estrutura vira (ex: Piso CAD)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Use o setor "Célula de Estruturas" para as estruturas.</t>
+          <t>vira_nome   - Nome da peca final</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>- No campo vira_peca, coloque o id_peca da peca CAD/GRC que ela se tornara.</t>
+          <t>vira_serial - Serial da peca final</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>- Ex: uma estrutura com vira_peca = "Piso CAD" aparece ligada ao Piso CAD no portal.</t>
+          <t>vira_data   - Data de fabricacao da peca final (dd/mm/aaaa)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>- Para pecas CAD/GRC normais, deixe vira_peca em branco.</t>
+      <c r="A22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>COMO FUNCIONA A ESTRUTURA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>- Cadastre a estrutura com setor "Célula de Estruturas".</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>- Preencha as 4 colunas vira_* com os dados da peca (Piso/Teto) que ela vira.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>- Ao receber a estrutura no CAD/GRC, o sistema cria a peca final "Faltando".</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>- Depois beneficia e bipa a peca final na conferencia/leitor -&gt; fica Disponivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>- Para pecas CAD/GRC normais, deixe as 4 colunas vira_* em branco.</t>
         </is>
       </c>
     </row>
